--- a/HDLBits_TODO.xlsx
+++ b/HDLBits_TODO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THZ\Desktop\HDLBITS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HDLBITS\HDLBITS-solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E9D510-E8D7-4BD3-9306-62A48C6DBBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1085B6-8321-4FF0-B55B-5008A16016BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -356,9 +356,6 @@
   </si>
   <si>
     <t>Karnaugh Map to Circuit</t>
-  </si>
-  <si>
-    <t>3-variable；4-variable 系列；Karnaugh map</t>
   </si>
   <si>
     <t>K-map 题全部独立完成</t>
@@ -1349,6 +1346,46 @@
         <family val="2"/>
       </rPr>
       <t>Truth tables</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3-variable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">4-variable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系列；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Karnaugh map</t>
     </r>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -1885,7 +1922,7 @@
       </c>
       <c r="B5" s="7">
         <f>COUNTIF(学习TODO!$J$6:$J$73,"已完成")</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C5" s="7">
         <f>COUNTIF(学习TODO!$J$6:$J$73,"进行中")</f>
@@ -1893,23 +1930,23 @@
       </c>
       <c r="D5" s="7">
         <f>COUNTIF(学习TODO!$J$6:$J$73,"未开始")</f>
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E5" s="8">
         <f>IF(A5=0,0,B5/A5)</f>
-        <v>7.3529411764705885E-2</v>
+        <v>0.19117647058823528</v>
       </c>
       <c r="F5" s="8">
         <f>IF(COUNTIF(学习TODO!$H$6:$H$73,"最高")=0,0,COUNTIFS(学习TODO!$H$6:$H$73,"最高",学习TODO!$J$6:$J$73,"已完成")/COUNTIF(学习TODO!$H$6:$H$73,"最高"))</f>
-        <v>4.7619047619047616E-2</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="G5" s="8">
         <f>IF(COUNTIF(学习TODO!$H$6:$H$73,"高")=0,0,COUNTIFS(学习TODO!$H$6:$H$73,"高",学习TODO!$J$6:$J$73,"已完成")/COUNTIF(学习TODO!$H$6:$H$73,"高"))</f>
-        <v>0.17391304347826086</v>
+        <v>0.34782608695652173</v>
       </c>
       <c r="H5" s="8">
         <f>IF(SUM(B9:B13)=0,0,SUM(C9:C13)/SUM(B9:B13))</f>
-        <v>8.9285714285714288E-2</v>
+        <v>0.23214285714285715</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1945,11 +1982,11 @@
       </c>
       <c r="C9" s="2">
         <f>COUNTIFS(学习TODO!$B$6:$B$73,A9,学习TODO!$J$6:$J$73,"已完成")</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D9" s="9">
         <f t="shared" ref="D9:D18" si="0">IF(B9=0,0,C9/B9)</f>
-        <v>0.35714285714285715</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>17</v>
@@ -2405,7 +2442,7 @@
         <v>70</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>71</v>
@@ -2479,7 +2516,7 @@
         <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>71</v>
@@ -2516,7 +2553,7 @@
         <v>75</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>71</v>
@@ -2553,7 +2590,7 @@
         <v>87</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>71</v>
@@ -2565,7 +2602,7 @@
         <v>88</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="3"/>
@@ -2602,7 +2639,7 @@
         <v>94</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="3"/>
@@ -2639,7 +2676,7 @@
         <v>98</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="3"/>
@@ -2676,7 +2713,7 @@
         <v>103</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="3"/>
@@ -2684,7 +2721,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" ht="16.5">
       <c r="A15" s="4">
         <v>10</v>
       </c>
@@ -2701,7 +2738,7 @@
         <v>106</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>383</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>71</v>
@@ -2710,10 +2747,10 @@
         <v>83</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="3"/>
@@ -2729,16 +2766,16 @@
         <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>106</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>71</v>
@@ -2747,10 +2784,10 @@
         <v>65</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="3"/>
@@ -2766,16 +2803,16 @@
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>106</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>71</v>
@@ -2784,10 +2821,10 @@
         <v>65</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="3"/>
@@ -2803,16 +2840,16 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>106</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>92</v>
@@ -2821,10 +2858,10 @@
         <v>93</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="3"/>
@@ -2840,16 +2877,16 @@
         <v>16</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>64</v>
@@ -2858,7 +2895,7 @@
         <v>93</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>5</v>
@@ -2877,16 +2914,16 @@
         <v>20</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>64</v>
@@ -2895,7 +2932,7 @@
         <v>65</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>5</v>
@@ -2914,16 +2951,16 @@
         <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>71</v>
@@ -2932,7 +2969,7 @@
         <v>83</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>5</v>
@@ -2951,16 +2988,16 @@
         <v>20</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>71</v>
@@ -2969,7 +3006,7 @@
         <v>83</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>5</v>
@@ -2988,16 +3025,16 @@
         <v>20</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>92</v>
@@ -3006,7 +3043,7 @@
         <v>93</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>5</v>
@@ -3025,16 +3062,16 @@
         <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>71</v>
@@ -3043,7 +3080,7 @@
         <v>65</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>5</v>
@@ -3062,25 +3099,25 @@
         <v>20</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="H25" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="I25" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>5</v>
@@ -3099,16 +3136,16 @@
         <v>20</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>92</v>
@@ -3117,7 +3154,7 @@
         <v>93</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>5</v>
@@ -3136,16 +3173,16 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>71</v>
@@ -3154,7 +3191,7 @@
         <v>83</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>5</v>
@@ -3173,16 +3210,16 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>71</v>
@@ -3191,7 +3228,7 @@
         <v>83</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>5</v>
@@ -3210,16 +3247,16 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>92</v>
@@ -3228,7 +3265,7 @@
         <v>65</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>5</v>
@@ -3247,16 +3284,16 @@
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>71</v>
@@ -3265,7 +3302,7 @@
         <v>83</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>5</v>
@@ -3284,16 +3321,16 @@
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="E31" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>64</v>
@@ -3302,7 +3339,7 @@
         <v>93</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>5</v>
@@ -3321,16 +3358,16 @@
         <v>24</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>92</v>
@@ -3339,7 +3376,7 @@
         <v>93</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>5</v>
@@ -3358,16 +3395,16 @@
         <v>24</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>71</v>
@@ -3376,7 +3413,7 @@
         <v>83</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>5</v>
@@ -3395,16 +3432,16 @@
         <v>24</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>71</v>
@@ -3413,7 +3450,7 @@
         <v>83</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>5</v>
@@ -3432,16 +3469,16 @@
         <v>27</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>71</v>
@@ -3450,7 +3487,7 @@
         <v>65</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>5</v>
@@ -3469,16 +3506,16 @@
         <v>27</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="F36" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>64</v>
@@ -3487,7 +3524,7 @@
         <v>93</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>5</v>
@@ -3506,16 +3543,16 @@
         <v>27</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>71</v>
@@ -3524,7 +3561,7 @@
         <v>65</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>5</v>
@@ -3543,16 +3580,16 @@
         <v>27</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>209</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>71</v>
@@ -3561,7 +3598,7 @@
         <v>83</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>5</v>
@@ -3580,16 +3617,16 @@
         <v>27</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="F39" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>64</v>
@@ -3598,7 +3635,7 @@
         <v>93</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>5</v>
@@ -3617,25 +3654,25 @@
         <v>27</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>5</v>
@@ -3654,16 +3691,16 @@
         <v>27</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="F41" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>71</v>
@@ -3672,7 +3709,7 @@
         <v>83</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>5</v>
@@ -3691,16 +3728,16 @@
         <v>27</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>71</v>
@@ -3709,7 +3746,7 @@
         <v>83</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>5</v>
@@ -3728,16 +3765,16 @@
         <v>27</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="E43" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>71</v>
@@ -3746,7 +3783,7 @@
         <v>83</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>5</v>
@@ -3765,16 +3802,16 @@
         <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="E44" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>235</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>92</v>
@@ -3783,7 +3820,7 @@
         <v>65</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>5</v>
@@ -3802,16 +3839,16 @@
         <v>27</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>71</v>
@@ -3820,7 +3857,7 @@
         <v>83</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>5</v>
@@ -3839,16 +3876,16 @@
         <v>27</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>71</v>
@@ -3857,7 +3894,7 @@
         <v>83</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>5</v>
@@ -3865,7 +3902,7 @@
       <c r="K46" s="5"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -3876,16 +3913,16 @@
         <v>27</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="F47" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>64</v>
@@ -3894,7 +3931,7 @@
         <v>65</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>5</v>
@@ -3913,16 +3950,16 @@
         <v>27</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="F48" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>71</v>
@@ -3931,7 +3968,7 @@
         <v>65</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>5</v>
@@ -3950,16 +3987,16 @@
         <v>27</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>92</v>
@@ -3968,7 +4005,7 @@
         <v>65</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>5</v>
@@ -3987,16 +4024,16 @@
         <v>27</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>262</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>92</v>
@@ -4005,7 +4042,7 @@
         <v>93</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>5</v>
@@ -4024,16 +4061,16 @@
         <v>30</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="F51" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>71</v>
@@ -4042,7 +4079,7 @@
         <v>83</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>5</v>
@@ -4061,16 +4098,16 @@
         <v>30</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>71</v>
@@ -4079,7 +4116,7 @@
         <v>65</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>5</v>
@@ -4098,16 +4135,16 @@
         <v>30</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="E53" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>275</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>71</v>
@@ -4116,7 +4153,7 @@
         <v>83</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>5</v>
@@ -4135,16 +4172,16 @@
         <v>30</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="E54" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>71</v>
@@ -4153,7 +4190,7 @@
         <v>83</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>5</v>
@@ -4172,16 +4209,16 @@
         <v>30</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>71</v>
@@ -4190,7 +4227,7 @@
         <v>83</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>5</v>
@@ -4209,16 +4246,16 @@
         <v>30</v>
       </c>
       <c r="C56" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="E56" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F56" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>287</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>64</v>
@@ -4227,7 +4264,7 @@
         <v>93</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>5</v>
@@ -4246,16 +4283,16 @@
         <v>30</v>
       </c>
       <c r="C57" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="E57" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F57" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>64</v>
@@ -4264,7 +4301,7 @@
         <v>93</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>5</v>
@@ -4283,16 +4320,16 @@
         <v>30</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="E58" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>296</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>92</v>
@@ -4301,7 +4338,7 @@
         <v>65</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>5</v>
@@ -4320,25 +4357,25 @@
         <v>30</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="E59" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="G59" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I59" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>5</v>
@@ -4357,16 +4394,16 @@
         <v>30</v>
       </c>
       <c r="C60" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="E60" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="F60" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>306</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>71</v>
@@ -4375,7 +4412,7 @@
         <v>83</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>5</v>
@@ -4383,7 +4420,7 @@
       <c r="K60" s="5"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="28">
@@ -4394,16 +4431,16 @@
         <v>30</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="E61" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="F61" s="3" t="s">
         <v>311</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>312</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>92</v>
@@ -4412,7 +4449,7 @@
         <v>65</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>5</v>
@@ -4431,16 +4468,16 @@
         <v>33</v>
       </c>
       <c r="C62" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="F62" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>64</v>
@@ -4449,7 +4486,7 @@
         <v>93</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>5</v>
@@ -4468,25 +4505,25 @@
         <v>33</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="E63" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="E63" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F63" s="3" t="s">
+      <c r="G63" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I63" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>5</v>
@@ -4505,16 +4542,16 @@
         <v>33</v>
       </c>
       <c r="C64" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>323</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>324</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>71</v>
@@ -4523,7 +4560,7 @@
         <v>65</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>5</v>
@@ -4542,16 +4579,16 @@
         <v>33</v>
       </c>
       <c r="C65" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="E65" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>329</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>92</v>
@@ -4560,7 +4597,7 @@
         <v>65</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>5</v>
@@ -4579,25 +4616,25 @@
         <v>33</v>
       </c>
       <c r="C66" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="E66" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="F66" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="G66" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="H66" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I66" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>336</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>5</v>
@@ -4616,25 +4653,25 @@
         <v>33</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="E67" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="E67" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F67" s="3" t="s">
+      <c r="G67" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I67" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>5</v>
@@ -4653,25 +4690,25 @@
         <v>33</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="E68" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I68" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>343</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>5</v>
@@ -4690,16 +4727,16 @@
         <v>33</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="E69" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>346</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>64</v>
@@ -4708,7 +4745,7 @@
         <v>65</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>5</v>
@@ -4727,25 +4764,25 @@
         <v>36</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="E70" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="E70" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F70" s="3" t="s">
+      <c r="G70" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I70" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>351</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>5</v>
@@ -4764,25 +4801,25 @@
         <v>39</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="E71" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F71" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="E71" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F71" s="3" t="s">
+      <c r="G71" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I71" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>5</v>
@@ -4801,25 +4838,25 @@
         <v>43</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="F72" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>359</v>
-      </c>
       <c r="G72" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H72" s="4" t="s">
         <v>93</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>5</v>
@@ -4838,25 +4875,25 @@
         <v>44</v>
       </c>
       <c r="C73" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="E73" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I73" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>5</v>
@@ -4922,16 +4959,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28">
@@ -4939,13 +4976,13 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4953,10 +4990,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>67</v>
@@ -4967,23 +5004,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>373</v>
-      </c>
       <c r="D4" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4994,20 +5031,20 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>377</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>378</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
